--- a/2026_全年打扫安排_周六外包.xlsx
+++ b/2026_全年打扫安排_周六外包.xlsx
@@ -4407,7 +4407,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>DMIS</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>CNS</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>NFE</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>HHU</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>DMIS</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>CHT</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>UNS</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>CNS</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>HHU</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>DMIS</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>NFE</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>CHT</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>UNS</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>CNS</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>HHU</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>DMIS</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>NFE</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>HHU</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Outsource</t>
+          <t>CNS</t>
         </is>
       </c>
     </row>
